--- a/statistics.xlsx
+++ b/statistics.xlsx
@@ -285,39 +285,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -575,9 +575,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="7.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="5" style="2" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="5" style="2" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1035,7 +1035,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>3</v>
@@ -1113,7 +1113,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>3</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B16" s="5" t="n">
         <f aca="false">SUM(E16:AB16)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>5</v>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>3</v>

--- a/statistics.xlsx
+++ b/statistics.xlsx
@@ -280,7 +280,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -315,6 +315,10 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1112,7 +1116,7 @@
       <c r="C13" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="9" t="s">
         <v>34</v>
       </c>
       <c r="E13" s="8" t="n">
@@ -1223,7 +1227,7 @@
       <c r="F16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="10" t="n">
         <v>6</v>
       </c>
       <c r="I16" s="8" t="n">

--- a/statistics.xlsx
+++ b/statistics.xlsx
@@ -170,9 +170,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -280,7 +281,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -290,6 +291,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -585,661 +590,664 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="3" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <f aca="false">SUM(E2:AB2)</f>
         <v>18</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U2" s="8" t="n">
+      <c r="G2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <f aca="false">SUM(E3:AB3)</f>
         <v>34</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="W3" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z3" s="7" t="n">
+      <c r="E3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z3" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <f aca="false">SUM(E4:AB4)</f>
         <v>22</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y4" s="8" t="n">
+      <c r="E4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <f aca="false">SUM(E5:AB5)</f>
         <v>14</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="8" t="n">
+      <c r="E5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <f aca="false">SUM(E6:AB6)</f>
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="W6" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="X6" s="8" t="n">
+      <c r="E6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <f aca="false">SUM(E7:AB7)</f>
         <v>19</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="S7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" s="8" t="n">
+      <c r="J7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <f aca="false">SUM(E8:AB8)</f>
         <v>12</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" s="8" t="n">
+      <c r="F8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <f aca="false">SUM(E9:AB9)</f>
         <v>16</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y9" s="8" t="n">
+      <c r="E9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <f aca="false">SUM(E10:AB10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <f aca="false">SUM(E11:AB11)</f>
         <v>15</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" s="8" t="n">
+      <c r="E11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <f aca="false">SUM(E12:AB12)</f>
         <v>19</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="7" t="n">
+      <c r="E12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <f aca="false">SUM(E13:AB13)</f>
         <v>13</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="7" t="n">
+      <c r="E13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <f aca="false">SUM(E14:AB14)</f>
         <v>18</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="8" t="n">
+      <c r="E14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <f aca="false">SUM(E15:AB15)</f>
         <v>7</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="C15" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="7" t="n">
+      <c r="E15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <f aca="false">SUM(E16:AB16)</f>
         <v>20</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="10" t="n">
+      <c r="E16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="I16" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" s="8" t="n">
+      <c r="I16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" s="9" t="n">
         <v>3</v>
       </c>
     </row>

--- a/statistics.xlsx
+++ b/statistics.xlsx
@@ -115,7 +115,7 @@
     <t xml:space="preserve">🔴</t>
   </si>
   <si>
-    <t xml:space="preserve">Авдеев Маским</t>
+    <t xml:space="preserve">Авдеев Максим</t>
   </si>
   <si>
     <t xml:space="preserve">Базир Ярослав</t>
@@ -281,7 +281,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -320,10 +320,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1124,7 +1120,7 @@
       <c r="C13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E13" s="9" t="n">
@@ -1235,7 +1231,7 @@
       <c r="F16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="10" t="n">
         <v>6</v>
       </c>
       <c r="I16" s="9" t="n">
